--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Value set for qualitative descriptions of genetic penetrance</t>
+    <t>Value set for qualitative descriptions of genetic penetrance, drawn from the HPO branch Inheritance qualifier (HP:0034335). Note that the graded terms (high/moderate/low penetrance) are subtypes of incomplete penetrance, not alternatives to complete penetrance.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -99,28 +99,40 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>HP:0034950</t>
+  </si>
+  <si>
+    <t>Typified by complete penetrance</t>
+  </si>
+  <si>
     <t>HP:0003829</t>
   </si>
   <si>
-    <t>Incomplete penetrance</t>
-  </si>
-  <si>
-    <t>HP:0003828</t>
-  </si>
-  <si>
-    <t>Variable penetrance</t>
-  </si>
-  <si>
-    <t>HP:0025169</t>
-  </si>
-  <si>
-    <t>Complete penetrance</t>
+    <t>Typified by incomplete penetrance</t>
+  </si>
+  <si>
+    <t>HP:4000158</t>
+  </si>
+  <si>
+    <t>Typified by high penetrance</t>
+  </si>
+  <si>
+    <t>HP:4000159</t>
+  </si>
+  <si>
+    <t>Typified by moderate penetrance</t>
+  </si>
+  <si>
+    <t>HP:4000160</t>
+  </si>
+  <si>
+    <t>Typified by low penetrance</t>
   </si>
   <si>
     <t>HP:0003831</t>
   </si>
   <si>
-    <t>Age-dependent penetrance</t>
+    <t>Typified by age-related disease onset</t>
   </si>
   <si>
     <t/>
@@ -391,7 +403,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -443,15 +455,31 @@
         <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>PenetranceValueSet</t>
+    <t>MII_VS_Seltene_Penetrance</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-seltene-penetrance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
